--- a/public/data3.xlsx
+++ b/public/data3.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ssean\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Semester 6\WebStory\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5764E756-47AA-4E40-BEDC-6A18FBB15B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452B7AE8-1C3C-433E-B1B0-5A74D21D736E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -165,7 +176,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -192,6 +203,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,10 +541,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S55"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="20.06640625" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" customWidth="1"/>
+    <col min="5" max="5" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -565,6 +577,7 @@
       <c r="D2" s="8">
         <v>345</v>
       </c>
+      <c r="E2" s="10"/>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7">
@@ -580,6 +593,7 @@
       <c r="D3" s="8">
         <v>13923</v>
       </c>
+      <c r="E3" s="10"/>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7">
@@ -997,6 +1011,7 @@
       <c r="D29" s="8">
         <v>770</v>
       </c>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:19">
       <c r="A30" s="5" t="s">
@@ -1011,6 +1026,7 @@
       <c r="D30" s="8">
         <v>31006</v>
       </c>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="5" t="s">
